--- a/inferences/residences-1701.xlsx
+++ b/inferences/residences-1701.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chekiang#Zhejiang 浙江， @wikidata: Q16967%CHEKIANG (actuel ZHEJIANG)</t>
+          <t>Chekiang#Zhejiang 浙江， @wikidata:Q16967%CHEKIANG (actuel ZHEJIANG)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Zhejiang 浙江， CHEKIANG (actuel ZHEJIANG)</t>
+          <t>Zhejiang 浙江，</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -549,7 +549,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="3">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hangzhou 杭州, </t>
+          <t>Hangzhou 杭州,</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="4">
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">海宁 </t>
+          <t>海宁</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="5">
@@ -725,7 +725,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiaxing 嘉兴, </t>
+          <t>Jiaxing 嘉兴,</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="6">
@@ -789,7 +789,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jinhua 金华, </t>
+          <t>Jinhua 金华,</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lanxi 兰溪, </t>
+          <t>Lanxi 兰溪,</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="8">
@@ -921,7 +921,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ningbo 宁波, </t>
+          <t>Ningbo 宁波,</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="9">
@@ -985,7 +985,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yinzhou 鄞州, </t>
+          <t>Yinzhou 鄞州,</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujian 福建, </t>
+          <t>Fujian 福建,</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="11">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuzhou 福州, </t>
+          <t>Fuzhou 福州,</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="12">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lianjiang 连江, </t>
+          <t>Lianjiang 连江,</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="13">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhangzhou 漳州, </t>
+          <t>Zhangzhou 漳州,</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quanzhou 泉州, </t>
+          <t>Quanzhou 泉州,</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="15">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xiamen 厦门, </t>
+          <t>Xiamen 厦门,</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="16">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Funing%(alors tcheou indépendant)Funing, @wikidata:Q241877, hoje Xiapu 霞浦</t>
+          <t>Funing%(alors tcheou indépendant)Funing, @wikidata:Q241877, today Xiapu 霞浦</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>(alors tcheou indépendant)Funing, , hoje Xiapu 霞浦</t>
+          <t>(alors tcheou indépendant)Funing, , today Xiapu 霞浦</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="17">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fu'an 福安, </t>
+          <t>Fu'an 福安,</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="18">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="19">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Kienning fou, Jianning 建寧,  (no coord.), using today's Jianyang wikidata:Q639862 coordinates:27°20'6"N, 118°6'58"E see 1644</t>
+          <t>Kienning fou, Jianning 建寧,  (no coord.), using today's Jianyang  coordinates:27°20'6"N, 118°6'58"E see 1644</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="20">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">浦城 </t>
+          <t>浦城</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="21">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaowu 邵武, </t>
+          <t>Shaowu 邵武,</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="22">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jianning Xian 建宁, </t>
+          <t>Jianning Xian 建宁,</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="23">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingzhou 汀州, </t>
+          <t>Tingzhou 汀州,</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="24">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">上杭 </t>
+          <t>上杭</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="25">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yanping 上杭, </t>
+          <t>Yanping 上杭,</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="26">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiangle 将乐, </t>
+          <t>Jiangle 将乐,</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="27">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henan 河南, </t>
+          <t>Henan 河南,</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="28">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaifeng 开封, </t>
+          <t>Kaifeng 开封,</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="29">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kweiteh#Guide, @wikidata:Q404817, hoje Shangqiu 商丘</t>
+          <t>Kweiteh#Guide, @wikidata:Q404817, today Shangqiu 商丘</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Guide, , hoje Shangqiu 商丘</t>
+          <t>Guide, , today Shangqiu 商丘</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="30">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>湖广 , for coordinates we use Wuchang District wikidata:Q1014420, where the head quarters of vice-roy of Huguang (wikidata:Q11563236) were located, coordinates: 30°33'23"N, 114°18'38"E(actuel HUNAN + HUBEI)Huguang</t>
+          <t>湖广 , for coordinates we use Wuchang District , where the head quarters of vice-roy of Huguang () were located, coordinates: 30°33'23"N, 114°18'38"E</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="31">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wuchang 武昌, </t>
+          <t>Wuchang 武昌,</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="32">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlu 安陆, </t>
+          <t>Anlu 安陆,</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="33">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">长沙 </t>
+          <t>长沙</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="34">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xiangtan 湘潭, </t>
+          <t>Xiangtan 湘潭,</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="35">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Chenzhou 郴州, Chen(g)chow</t>
+          <t>Chenzhou 郴州,</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="36">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hengyang 衡阳, </t>
+          <t>Hengyang 衡阳,</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="37">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jingzhou 荆州, </t>
+          <t>Jingzhou 荆州,</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="38">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="39">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yongzhou 永州, </t>
+          <t>Yongzhou 永州,</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="40">
@@ -2977,7 +2977,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="41">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nanjing 南京, </t>
+          <t>Nanjing 南京,</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="42">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anqing 安庆, </t>
+          <t>Anqing 安庆,</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="43">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Changzhou 常州, </t>
+          <t>Changzhou 常州,</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="44">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wuxi 无锡, </t>
+          <t>Wuxi 无锡,</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="45">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chizhou 池州, Chinchow (= Kweichih)</t>
+          <t>Chizhou 池州,</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="46">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjiang 镇江, </t>
+          <t>Zhenjiang 镇江,</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="47">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danyang 丹阳, </t>
+          <t>Danyang 丹阳,</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="48">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">凤阳, </t>
+          <t>凤阳,</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="49">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wuhe 五河, </t>
+          <t>Wuhe 五河,</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="50">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huai'an 淮安, </t>
+          <t>Huai'an 淮安,</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="51">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suzhou 苏州, </t>
+          <t>Suzhou 苏州,</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="52">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Changshu (Cham xo), Changshu 常熟, </t>
+          <t>Changshu (Cham xo), Changshu 常熟,</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="53">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">昆山, </t>
+          <t>昆山,</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="54">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xuzhou 徐州, </t>
+          <t>Xuzhou 徐州,</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="55">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Songjiang 松江, </t>
+          <t>Songjiang 松江,</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="56">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shanghai 上海, </t>
+          <t>Shanghai 上海,</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="57">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qingpu, </t>
+          <t>Qingpu,</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="58">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taicang 太仓, </t>
+          <t>Taicang 太仓,</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="59">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiading 嘉定, </t>
+          <t>Jiading 嘉定,</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="60">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chongming 崇明, </t>
+          <t>Chongming 崇明,</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="61">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yangzhou 扬州, </t>
+          <t>Yangzhou 扬州,</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="62">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiangxi 江西, </t>
+          <t>Jiangxi 江西,</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -4409,7 +4409,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="63">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nanchang 南昌, </t>
+          <t>Nanchang 南昌,</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="64">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuzhou 抚州, </t>
+          <t>Fuzhou 抚州,</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="65">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="66">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ganzhou (赣州) in Jiangxi </t>
+          <t>Ganzhou (赣州) in Jiangxi</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="67">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ningdu 宁都, </t>
+          <t>Ningdu 宁都,</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="68">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xinfeng 信丰, </t>
+          <t>Xinfeng 信丰,</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="69">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ji'an 吉安, </t>
+          <t>Ji'an 吉安,</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="70">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dingnan 定南, </t>
+          <t>Dingnan 定南,</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="71">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jianchang 建昌, </t>
+          <t>Jianchang 建昌,</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="72">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nanfeng 南丰, </t>
+          <t>Nanfeng 南丰,</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="73">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiujiang 九江, </t>
+          <t>Jiujiang 九江,</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="74">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guangxin 广信, </t>
+          <t>Guangxin 广信,</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="75">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">玉山, </t>
+          <t>玉山,</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="76">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nan'an 南安, </t>
+          <t>Nan'an 南安,</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="77">
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="78">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guangxi 广西, </t>
+          <t>Guangxi 广西,</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -5445,7 +5445,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="79">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guilin 桂林, </t>
+          <t>Guilin 桂林,</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="80">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wuzhou 梧州, </t>
+          <t>Wuzhou 梧州,</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="81">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guangdong 广东, </t>
+          <t>Guangdong 广东,</t>
         </is>
       </c>
       <c r="J81" t="inlineStr"/>
@@ -5625,7 +5625,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="82">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Guangzhou 广州, Canton</t>
+          <t>Guangzhou 广州,</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="83">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foshan 佛山, </t>
+          <t>Foshan 佛山,</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="84">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xinhui 新会, </t>
+          <t>Xinhui 新会,</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="85">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dongguan 东莞, </t>
+          <t>Dongguan 东莞,</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="86">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>琼州, Kiungchow (île de Hainan), Qiongzhou</t>
+          <t>琼州,</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="87">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="88">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leizhou 雷州, </t>
+          <t>Leizhou 雷州,</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="89">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nanxiong 南雄, </t>
+          <t>Nanxiong 南雄,</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="90">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Shihing#Shixing 始兴, @wikidata: Q1346567</t>
+          <t>Shihing#Shixing 始兴, @wikidata:Q1346567</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shixing 始兴, </t>
+          <t>Shixing 始兴,</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="91">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xunte Shunde 顺德, </t>
+          <t>Xunte Shunde 顺德,</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="92">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>(confirm same as 1641 deh-r1644-shiuchow) @dehergne:n402 (p.359) Chao-tcheou, today Shaozhou, 韶州, , historical administrative division. The administrative center was Qujiang 曲江, wikidata:Q1346617, coordinates:24°40'58"N, 113°36'1"E, which is in the present-day City of Shaoguan 韶关.Shiuhow (Xao cheu)</t>
+          <t>(confirm same as 1641 deh-r1644-shiuchow) @dehergne:n402 (p.359) Chao-tcheou, today Shaozhou, 韶州, , historical administrative division. The administrative center was Qujiang 曲江, , coordinates:24°40'58"N, 113°36'1"E, which is in the present-day City of Shaoguan 韶关.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="93">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lecong 乐从, </t>
+          <t>Lecong 乐从,</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="94">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>(confirmar) Gaimushuo 1943 "Yanfa-hsien 仁化祭, 廣東省北部 (曲江味)の 東北(Jenhua)", wikipedia entry for Renhua County () gives Yanfa as postal code 仁化县 (仁化縣) coordinates: 25°5'22"N, 113°44'41"EYanfa -- Gin hoa</t>
+          <t>(confirmar) Gaimushuo 1943 "Yanfa-hsien 仁化祭, 廣東省北部 (曲江味)の 東北(Jenhua)", wikipedia entry for Renhua County () gives Yanfa as postal code 仁化县 (仁化縣) coordinates: 25°5'22"N, 113°44'41"E</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="95">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chao Kim, Zhaoqing 肇庆, </t>
+          <t>Chao Kim, Zhaoqing 肇庆,</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="96">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Huizhou,惠州 Waichow, Hwaichow (Hoei cheu), Guizhou,</t>
+          <t>Huizhou,惠州</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="97">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macao 澳门, </t>
+          <t>Macao 澳门,</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="98">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilha Verde, </t>
+          <t>Ilha Verde,</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="99">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lapa (Wan-tchai),Wanzai, </t>
+          <t>Lapa (Wan-tchai),Wanzai,</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="100">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">KWEICHOW (actuel GUIZHOU): néant Guizhou 贵州, </t>
+          <t>KWEICHOW (actuel GUIZHOU): néant Guizhou 贵州,</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
@@ -6865,7 +6865,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="101">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pequim#@wikidata: Q956%PEKING (actuel HEBEI) 北京</t>
+          <t>Pequim#@wikidata:Q956%PEKING (actuel HEBEI) 北京</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6917,7 +6917,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="102">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Beijing 北京, Pékin collège St Joseph (1605) ou Si-t'ang (sera appelé Nan-t'ang en 1723, à cause du Si-t'ang fondé pour la Propagande, R)</t>
+          <t>Beijing 北京,</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="103">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Xitang 西堂  西堂Si-t'ang fondé pour la Propagande, R [em 1703])</t>
+          <t>Xitang 西堂  西堂</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="104">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Dongtang 东堂  东堂Tong-t'ang ou R Saint-Joseph (1655)</t>
+          <t>Dongtang 东堂  东堂</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="105">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beitang, 北堂 </t>
+          <t>Beitang, 北堂</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="106">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liangxiang 良乡, </t>
+          <t>Liangxiang 良乡,</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="107">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tongzhou 通州, </t>
+          <t>Tongzhou 通州,</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="108">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhengding 正定, </t>
+          <t>Zhengding 正定,</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="109">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baoding 保定, </t>
+          <t>Baoding 保定,</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="110">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shanxi 山西, </t>
+          <t>Shanxi 山西,</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -7501,7 +7501,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="111">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiyuan 太原, </t>
+          <t>Taiyuan 太原,</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="112">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="113">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pingyao du Fenchow 平遥, </t>
+          <t>Pingyao du Fenchow 平遥,</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="114">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Jiexiu 介休, Kiehsiu du Fenchow</t>
+          <t>Jiexiu 介休,</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="115">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Pingyang Fu, . Now it is in Linfen 临汾 wikidata:Q73156, coordinates:36°4'52"N, 111°30'31"E</t>
+          <t>Pingyang Fu, . Now it is in Linfen 临汾 , coordinates:36°4'52"N, 111°30'31"E</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="116">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiangzhou, </t>
+          <t>Jiangzhou,</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="117">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puzhou 绛州, </t>
+          <t>Puzhou 绛州,</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="118">
@@ -8033,7 +8033,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="119">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Xiangling 襄陵县，, (no coord.), can be substituted by Q1197358, present day Xiangfen County 襄汾县, coordinates: 35°52'38"N, 111°25'54"EDe Pingyang dépendaient les «templa et forté parvae domus» dont parle la Liste 1701 à Hungtung, Kiehsiu, Siangling, Tàiping et Wanchuian, qui, à nos yeux, sont des chrétientés, non des R, de même que Tsinglo du Sinchow indépendant</t>
+          <t>Xiangling 襄陵县，, (no coord.), can be substituted by Q1197358, present day Xiangfen County 襄汾县, coordinates: 35°52'38"N, 111°25'54"E</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="120">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Taiping 太平县， (no coord.), can be substituted by Q11137509，the present-day 汾城镇 (coordinates:35°49'8"N, 111°16'25"E)De Pingyang dépendaient les «templa et forté parvae domus» dont parle la Liste 1701 à Hungtung, Kiehsiu, Siangling, Tàiping et Wanchuian, qui, à nos yeux, sont des chrétientés, non des R, de même que Tsinglo du Sinchow indépendant</t>
+          <t>Taiping 太平县， (no coord.), can be substituted by Q11137509，the present-day 汾城镇 (coordinates:35°49'8"N, 111°16'25"E)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="121">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wanquan 万泉县，the wikidata code of it does not contain coordinate information, which can be substituted by Q1196908, the present-day万荣县 (35°25'1"N, 110°49'52"E), </t>
+          <t>Wanquan 万泉县，the wikidata code of it does not contain coordinate information, which can be substituted by Q1196908, the present-day万荣县 (35°25'1"N, 110°49'52"E),</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="122">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xinzhou 忻州, </t>
+          <t>Xinzhou 忻州,</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="123">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jingle 静乐, </t>
+          <t>Jingle 静乐,</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="124">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">actuel Shandong, Shandong 山东, </t>
+          <t>actuel Shandong, Shandong 山东,</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -8421,7 +8421,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="125">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jinan 济南, </t>
+          <t>Jinan 济南,</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="126">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tai'an 泰安, </t>
+          <t>Tai'an 泰安,</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="127">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dezhou 德州, </t>
+          <t>Dezhou 德州,</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="128">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">(-- Idu, Yitu)Qingzhou 青州, , Yidu, </t>
+          <t>(-- Idu, Yitu)Qingzhou 青州, , Yidu,</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="129">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linkiu 临朐, </t>
+          <t>Linkiu 临朐,</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="130">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dungchang 东昌, </t>
+          <t>Dungchang 东昌,</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="131">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linqing 临清, </t>
+          <t>Linqing 临清,</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="132">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yanzhou 兖州, </t>
+          <t>Yanzhou 兖州,</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="133">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ichow#(hoje Linyi, Shandong) 沂州, @wikidata:Q11552388%Ichow (-- Lini), alors tcheou</t>
+          <t>Ichow#(today Linyi, Shandong) 沂州, @wikidata:Q11552388%Ichow (-- Lini), alors tcheou</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>(hoje Linyi, Shandong) 沂州, Ichow (-- Lini), alors tcheou</t>
+          <t>(today Linyi, Shandong) 沂州,</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="134">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jining 济宁, </t>
+          <t>Jining 济宁,</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="135">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shensi#Hoje Shaanxi para distinguir de deh-r1701-shansi @wikidata:Q47974%(actuel SHANXI)Shanxi</t>
+          <t>Shensi#Today Shaanxi to distinguish from deh-r1701-shansi @wikidata:Q47974%(actuel SHANXI)Shanxi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Hoje Shaanxi para distinguir de deh-r1701-shansi (actuel SHANXI)Shanxi</t>
+          <t>Today Shaanxi to distinguish from deh-r1701-shansi</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -9133,7 +9133,7 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="136">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xi'an 西安, </t>
+          <t>Xi'an 西安,</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="137">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanyuan 三原, </t>
+          <t>Sanyuan 三原,</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="138">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanzhong 汉中, </t>
+          <t>Hanzhong 汉中,</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="139">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chenggu 城固, </t>
+          <t>Chenggu 城固,</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="140">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>(?)No wikidata, Dehergne 1957 «Il y a aussi une chrétienté à "Siao tchai tse" , 小塞子, "Siao tsai pe" près de Chengku. Vers 1635, le yays est délivré par deux fois des sauterelles, grâce aux prières du P. Le Fèvre, qui a une florissante chrétienté à Siao tchai tseSiao-tchai du Chengku</t>
+          <t>(?)No wikidata, Dehergne 1957 «Il y a aussi une chrétienté à "Siao tchai tse" , 小塞子, "Siao tsai pe" près de Chengku. Vers 1635, le yays est délivré par deux fois des sauterelles, grâce aux prières du P. Le Fèvre, qui a une florissante chrétienté à Siao tchai tse</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="141">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">actuel SICHUAN)Sichuan 四川, </t>
+          <t>actuel SICHUAN)Sichuan 四川,</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -9513,7 +9513,7 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="142">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chengdu 成都, </t>
+          <t>Chengdu 成都,</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="143">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chongqing 重庆, </t>
+          <t>Chongqing 重庆,</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="144">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yunnan 云南, </t>
+          <t>Yunnan 云南,</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
@@ -9693,7 +9693,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="145">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yunanfu,present day Kunming 昆明, </t>
+          <t>Yunanfu,present day Kunming 昆明,</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
-        <v>11701644</v>
+        <v>1701</v>
       </c>
     </row>
   </sheetData>
